--- a/data/trans_camb/IP1007-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,13</t>
+          <t>-5,43; 2,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 0,0</t>
+          <t>-7,38; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,03</t>
+          <t>-2,53; 0,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,04</t>
+          <t>-2,52; 1,04</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,5</t>
+          <t>-4,6; -0,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,5</t>
+          <t>-4,6; -0,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,26</t>
+          <t>-2,19; -0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,28</t>
+          <t>-1,73; 1,33</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,0</t>
+          <t>-2,66; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,0</t>
+          <t>-1,38; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,0</t>
+          <t>-1,38; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-1,59; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,71; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,85</t>
+          <t>-0,92; 1,88</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,0</t>
+          <t>-1,23; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,78</t>
+          <t>-0,82; 0,62</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,45</t>
+          <t>-0,44; 0,4</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,49</t>
+          <t>-0,44; 0,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,01</t>
+          <t>-0,87; -0,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,26</t>
+          <t>-0,71; 0,26</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,07</t>
+          <t>-0,52; 0,09</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,15</t>
+          <t>-0,46; 0,18</t>
         </is>
       </c>
     </row>
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 238,65</t>
+          <t>-100,0; 247,82</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,49</t>
+          <t>-100,0; 95,99</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-86,78; 130,64</t>
+          <t>-88,13; 148,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Provincia-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,17</t>
+          <t>-5,35; 2,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 0,0</t>
+          <t>-6,54; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,98</t>
+          <t>-2,56; 0,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,04</t>
+          <t>-2,62; 1,05</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,51</t>
+          <t>-4,58; -0,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,51</t>
+          <t>-4,58; -0,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; -0,26</t>
+          <t>-2,24; -0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 1,33</t>
+          <t>-1,5; 1,35</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,0; 6,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,85</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-2,67; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>-2,68; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,0</t>
+          <t>-1,59; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,0</t>
+          <t>-1,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-1,98; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,0</t>
+          <t>-2,39; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,88</t>
+          <t>-0,91; 1,57</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,0</t>
+          <t>-1,57; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,62</t>
+          <t>-0,85; 0,63</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,4</t>
+          <t>-0,42; 0,45</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,42</t>
+          <t>-0,43; 0,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,87; -0,0</t>
+          <t>-0,92; 0,01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,26</t>
+          <t>-0,74; 0,25</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,09</t>
+          <t>-0,53; 0,05</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,18</t>
+          <t>-0,45; 0,17</t>
         </is>
       </c>
     </row>
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 247,82</t>
+          <t>-100,0; 199,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,99</t>
+          <t>-100,0; 66,63</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 148,31</t>
+          <t>-87,82; 124,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-1,06</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-2,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 0,0</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,31; 2,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>-7,51; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,99</t>
+          <t>-2,49; 1,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,05</t>
+          <t>-2,41; 1,04</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-49,76%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,12</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,52; -0,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>-4,52; -0,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; -0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; -0,5</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,26</t>
+          <t>-2,42; -0,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,35</t>
+          <t>-1,5; 1,28</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,15</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,75; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,46; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-1,47; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,0</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,39</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,39</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-0,93; 1,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,0</t>
+          <t>-2,47; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,57</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,0</t>
+          <t>-1,26; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,63</t>
+          <t>-0,81; 0,78</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>80,67%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>80,67%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,19</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>-0,91; 0,01</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-0,75; 0,26</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>-0,42; 0,45</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-0,43; 0,41</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 0,01</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,25</t>
+          <t>-0,44; 0,49</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,05</t>
+          <t>-0,54; 0,07</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,17</t>
+          <t>-0,48; 0,15</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-79,68%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-42,0%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-18,88%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-35,28%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-79,68%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-42,0%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 238,65</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 199,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,63</t>
+          <t>-100,0; 75,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-87,82; 124,97</t>
+          <t>-86,78; 130,64</t>
         </is>
       </c>
     </row>
